--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1392,792 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129232446</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97530</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>634988</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6960792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129232443</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56913</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>634988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6960648</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129208721</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92855</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>635018</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6960696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129232449</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>634876</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960855</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129232444</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91981</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635006</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6960631</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129232445</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>634971</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6960858</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 exemplar</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129232448</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>634852</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6960839</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129232450</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>635059</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6960642</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129209281</v>
+        <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634720</v>
+        <v>634816</v>
       </c>
       <c r="R3" t="n">
-        <v>6960743</v>
+        <v>6960740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129209795</v>
+        <v>129209281</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634816</v>
+        <v>634720</v>
       </c>
       <c r="R4" t="n">
-        <v>6960740</v>
+        <v>6960743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129209281</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129210028</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129209702</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>129208524</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129232443</v>
       </c>
       <c r="B10" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129232449</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>129232448</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129232450</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129209281</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129210028</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129209702</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>129208524</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129232443</v>
       </c>
       <c r="B10" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129232449</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>129232448</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129232450</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129232448</v>
+        <v>129232450</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634852</v>
+        <v>635059</v>
       </c>
       <c r="R15" t="n">
-        <v>6960839</v>
+        <v>6960642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129232450</v>
+        <v>129232448</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635059</v>
+        <v>634852</v>
       </c>
       <c r="R16" t="n">
-        <v>6960642</v>
+        <v>6960839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129232450</v>
+        <v>129232448</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635059</v>
+        <v>634852</v>
       </c>
       <c r="R15" t="n">
-        <v>6960642</v>
+        <v>6960839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129232448</v>
+        <v>129232450</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634852</v>
+        <v>635059</v>
       </c>
       <c r="R16" t="n">
-        <v>6960839</v>
+        <v>6960642</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129232449</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>129232448</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129232450</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129232449</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>129232448</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129232450</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129209795</v>
+        <v>129209281</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634816</v>
+        <v>634720</v>
       </c>
       <c r="R3" t="n">
-        <v>6960740</v>
+        <v>6960743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129209281</v>
+        <v>129209795</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634720</v>
+        <v>634816</v>
       </c>
       <c r="R4" t="n">
-        <v>6960743</v>
+        <v>6960740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129209281</v>
+        <v>129209795</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634720</v>
+        <v>634816</v>
       </c>
       <c r="R3" t="n">
-        <v>6960743</v>
+        <v>6960740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129209795</v>
+        <v>129209281</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634816</v>
+        <v>634720</v>
       </c>
       <c r="R4" t="n">
-        <v>6960740</v>
+        <v>6960743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129232448</v>
+        <v>129232450</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>634852</v>
+        <v>635059</v>
       </c>
       <c r="R15" t="n">
-        <v>6960839</v>
+        <v>6960642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129232450</v>
+        <v>129232448</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635059</v>
+        <v>634852</v>
       </c>
       <c r="R16" t="n">
-        <v>6960642</v>
+        <v>6960839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129232450</v>
+        <v>129232448</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635059</v>
+        <v>634852</v>
       </c>
       <c r="R15" t="n">
-        <v>6960642</v>
+        <v>6960839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129232448</v>
+        <v>129232450</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>634852</v>
+        <v>635059</v>
       </c>
       <c r="R16" t="n">
-        <v>6960839</v>
+        <v>6960642</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129210204</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129209795</v>
+        <v>129209281</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634816</v>
+        <v>634720</v>
       </c>
       <c r="R3" t="n">
-        <v>6960740</v>
+        <v>6960743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129209281</v>
+        <v>129209795</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storhögen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634720</v>
+        <v>634816</v>
       </c>
       <c r="R4" t="n">
-        <v>6960743</v>
+        <v>6960740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>129210028</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129209702</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>129209156</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>129208524</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129232446</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129232443</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129208721</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129232449</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129232444</v>
       </c>
       <c r="B13" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129232445</v>
       </c>
       <c r="B14" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>129232448</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129232450</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,113 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129878244</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storhögen, Storhögen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>634964</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6960808</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>129878244</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>129878244</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>129878244</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>129878244</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34546-2025 artfynd.xlsx
+++ b/artfynd/A 34546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129208439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129209156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129209795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232444</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129210204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129208721</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232449</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232450</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129208524</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129209281</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129209702</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129210028</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129878244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232443</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,8 +2466,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129232446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>